--- a/光伏配储项目/电价数据/2026/璧青湾升压站.xlsx
+++ b/光伏配储项目/电价数据/2026/璧青湾升压站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.55438</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.64728</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1.05028</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.16692</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.1455</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.11133</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.9893</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.99329</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44107</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.6522</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.70529</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.63774</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.97742</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.9775199999999999</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.97341</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.63106</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.9848300000000001</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.98077</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.96533</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.97597</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.6674099999999999</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.98194</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39496</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.65995</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.9811299999999999</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.98672</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.68798</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>1.01147</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>1.09749</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.40384</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.87481</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.6874600000000001</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.68326</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.31292</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.46334</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.74882</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.77207</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.40351</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.3867</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.03526</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>1.02043</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>1.11258</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.75885</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.71593</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.51258</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.40994</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.40654</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.4101</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.7908500000000001</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.97117</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.33864</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.53088</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.77546</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.45103</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.7836000000000001</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.75927</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.98148</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.9122400000000001</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>1.0677</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.33857</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.16692</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.18466</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.74233</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.23051</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>1.18494</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>1.10426</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.24529</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.54424</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.19873</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.26888</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.49245</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.32433</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.25261</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.43984</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.37022</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.30099</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.81151</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47986</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.41038</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41279</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42199</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.18154</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.04915</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.18243</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5376799999999999</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52274</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5064</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5143300000000001</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.7277899999999999</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.6288400000000001</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.7020599999999999</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.6075499999999999</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.60009</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.6868099999999999</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.64622</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.6504</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.6504</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.64613</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.6377699999999999</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.69464</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.9610599999999999</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.29999</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.96101</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.70548</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.60077</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.6620199999999999</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.56902</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.5907100000000001</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.9495</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.16458</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.78831</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.13383</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.05049</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>1.00483</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.7161000000000001</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.54938</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.5713200000000001</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.68555</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.18569</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.24425</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.49077</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.31003</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1.18476</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.66076</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1.08939</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.8334900000000001</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.26231</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.15698</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.2877</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.62395</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.63786</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.56545</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.6185</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.18583</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>1.18461</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.1844</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.18561</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.9923</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.18743</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.18773</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.18514</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.67994</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.18764</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.21361</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.24392</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.54227</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.4494</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.18756</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.51193</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.27185</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.74733</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.76295</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.92064</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.4401</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33631</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.68708</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.83913</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.81165</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.59982</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.67738</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.58996</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1.27285</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.80089</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.8012999999999999</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.7590800000000001</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.67952</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.81687</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.6406499999999999</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.79577</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.58166</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.37245</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.67648</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.59675</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.66861</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.6435</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.6288899999999999</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.6445299999999999</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.6490199999999999</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.58061</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.70129</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.83939</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.11651</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.89847</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.76425</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.72582</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.6392100000000001</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.65028</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.4382</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.75979</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.18486</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.55371</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.72496</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.19608</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.65067</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.19377</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>1.18417</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.79835</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.95668</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.18456</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1.18451</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.90173</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.56247</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.42074</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.47728</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.67814</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.18573</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>1.04289</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.18468</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.42105</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.25841</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.18474</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.21898</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.21318</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.4257</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.27896</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.29957</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.66548</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.19502</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.19703</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1.05764</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>1.09302</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.11413</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.10012</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.22459</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.18477</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.26834</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>1.0113</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.76332</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.71999</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.5349400000000001</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.41302</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3432</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.16665</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.8663200000000001</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.8559600000000001</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.8169099999999999</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.9873099999999999</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.67314</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.77111</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.66714</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.85341</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.7975800000000001</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.74942</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.6524500000000001</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.6495299999999999</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.4914</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.57045</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.49121</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.5130800000000001</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.66122</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.65434</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.7641699999999999</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.64335</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.6099199999999999</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.56999</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.52547</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.68289</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.7254700000000001</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.93831</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.18453</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.18526</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.85172</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.56894</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.6648</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.90287</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.8797999999999999</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.15961</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.42585</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.77239</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.96989</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.22792</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.69689</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.12288</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.5243099999999999</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.48748</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.6585599999999999</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>1.00177</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.11026</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.25773</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.18404</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1.08231</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>1.00029</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>1.03339</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.99736</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.28777</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.47007</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.8105599999999999</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.37321</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.22642</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.8627100000000001</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>1.10085</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1.18206</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>1.13199</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>1.18307</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.2805</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.34162</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.18309</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.29445</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.20139</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.19214</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.18708</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>1.21165</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>1.22154</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>1.20718</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1.18269</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1.18546</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.7367400000000001</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.52788</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.74601</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.3217</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.7487699999999999</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.4942</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.40118</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.33669</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.47925</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.50947</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.5249299999999999</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.4031</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.46052</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.4301</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.4599</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.72126</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.8541599999999999</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.61779</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.70596</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.73075</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.8541599999999999</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.71113</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.55279</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.55279</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.5434500000000001</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.47657</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.09891</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.28652</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.28292</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.5508200000000001</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.48482</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.5169400000000001</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.46863</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.6468200000000001</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.51112</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.4904</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.4031</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.49588</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.49625</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.61258</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.4080299999999999</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.5142899999999999</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.51349</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.41162</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.49132</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35472</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.41045</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46752</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40443</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34421</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.20945</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.99113</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1.00634</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.59765</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.73542</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.69359</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.6453</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.6932999999999999</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.68091</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.68029</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.97663</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.68643</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.68669</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.67974</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.67977</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.27659</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.07464</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.30569</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04711</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04874</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.03957</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.26915</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.07809999999999999</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.28883</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.12382</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.00382</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.3017</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.2997</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.3037</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.25999</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.28434</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.28956</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.29304</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.38918</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.42951</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.45009</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.7144299999999999</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.69198</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.36274</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.39357</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.38878</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.36405</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.39375</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.70094</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.6922999999999999</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.6921</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.39692</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33409</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.68133</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.59861</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40508</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.27546</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30637</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.30436</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.30818</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.30234</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.28688</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.28339</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1686</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14582</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15718</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15646</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.2327</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.2119</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.29055</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.2717</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.38954</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.76239</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.89858</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.6964199999999999</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.6964</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.7029500000000001</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.7666000000000001</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.9759099999999999</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.44414</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.36776</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.49527</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.74661</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.91699</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.67477</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.54474</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.48468</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.45532</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.09251999999999999</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.30559</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.7474</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.74576</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.64695</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.6097100000000001</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.48067</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.7379199999999999</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79059</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.78955</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.60891</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.7521</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>1.02854</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.42684</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.85794</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.4574</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.34257</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.81187</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.40565</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>1.0622</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.42403</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.78786</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.46422</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.7887799999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.8042</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78808</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8807999999999999</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50556</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41511</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41562</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46401</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.22273</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5511200000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6430800000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54212</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.7313200000000001</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.70861</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.70078</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.70428</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.7067100000000001</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.6226499999999999</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.70725</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.69929</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.58356</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.5834900000000001</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.5943999999999999</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38721</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.69186</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.68053</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.68352</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.68232</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.6817000000000001</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.69533</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.6820499999999999</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.6799700000000001</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.58517</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.72768</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.5834900000000001</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.6003500000000001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43717</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59596</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.56429</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66877</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.07815</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.6545</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.52828</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.57538</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.59683</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.96409</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.3384</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.30702</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.28182</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.57043</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.80028</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.5770599999999999</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.6553099999999999</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.5569</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>1.00948</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.78912</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.7339</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.6426000000000001</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.5817599999999999</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>1.00786</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>1.06963</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.55753</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.71726</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.68213</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.74583</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.6701699999999999</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.71676</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.8227300000000001</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.70717</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.7165900000000001</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.60519</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.5910599999999999</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.71558</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.72611</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.74537</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.75395</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.78047</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.74976</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.78647</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.75352</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.74988</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.7510800000000001</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.7465499999999999</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.7423200000000001</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.72736</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.74194</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.7181000000000001</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.69284</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.7255199999999999</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.69733</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.70716</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.6979099999999999</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.6921</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.5832200000000001</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9511799999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.67652</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.80492</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.7837499999999999</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.83588</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.68198</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.68643</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.61546</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.65498</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.5835</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.6604</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.41122</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.52944</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.62737</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.74566</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.8944500000000001</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.14598</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.9391499999999999</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.5579299999999999</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.12355</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.86378</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.97104</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.8807999999999999</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.65174</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.83382</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>1.09206</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.6794199999999999</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.5323600000000001</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.40232</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.37548</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.89444</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>1.12459</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.79614</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1.22621</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.80353</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.83445</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.86505</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.75688</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.40732</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.39197</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.35221</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37613</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.47751</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.39704</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.38471</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.36477</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.44457</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.37096</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.3976</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.50038</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43244</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.42025</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.35374</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.41573</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44782</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.4204</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59663</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.19973</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.51493</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7027</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79415</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6489400000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5828300000000001</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43956</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43711</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42768</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39608</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.73125</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.42728</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.75683</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.1763</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.9220700000000001</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.65638</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.79181</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.7092200000000001</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.55906</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.59836</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.11219</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.6112</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.90259</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.59561</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.40199</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.37843</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.34423</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.34339</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>1.62955</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.9358200000000001</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.53398</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.5936699999999999</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.8645700000000001</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.52486</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.75809</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>1.07235</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>1.09388</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.9349400000000001</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.9953500000000001</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.94747</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.18463</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1.18119</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.8856799999999999</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>1.18142</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.62836</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.99414</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>1.03848</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>1.18131</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.9746900000000001</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>1.0155</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.57691</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.93899</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>1.00436</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>1.05981</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.90937</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.88855</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.68206</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>1.12143</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.60446</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.9836900000000001</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>1.01988</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.7579400000000001</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.33864</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.77707</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.6409400000000001</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.64216</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.34156</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.62071</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.5348200000000001</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.67635</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.38721</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.7955399999999999</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.6409900000000001</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.6048300000000001</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.64048</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.6090099999999999</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.65612</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.41673</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.75062</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.68424</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>1.00695</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>1.2363</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.68426</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.68459</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.68432</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.6244</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.6148400000000001</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.67822</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.68425</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.56556</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.55536</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.56896</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.5740499999999999</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.37187</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.6915</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.37855</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.40281</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.6334299999999999</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.62018</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39374</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39799</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45668</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43939</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.62097</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.61997</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.6196499999999999</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34932</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5814600000000001</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.50724</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46858</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.4237</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41597</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.5449299999999999</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.7616499999999999</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.68552</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.68826</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.6829</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.7049299999999999</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.6122000000000001</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.64789</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.5327000000000001</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.45743</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.53216</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.45743</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.65752</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.6889500000000001</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.6856</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.66627</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.60951</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.60422</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.56917</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.59238</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.3424700000000001</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.39087</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.33248</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.30866</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.48311</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.36848</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.3756</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.41233</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.48839</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.69926</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.59996</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.62685</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.85053</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.26847</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.16593</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.85053</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.42974</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.7002200000000001</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.95056</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.18435</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.13312</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.13047</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.5501200000000001</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.43883</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.4292</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.3971</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.37948</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39127</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.49783</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.44676</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.41416</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.42556</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.4201</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37043</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.5656100000000001</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.57097</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.56878</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.57097</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.53426</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.66055</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.45994</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.53376</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.45898</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.5355</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.59421</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.6625700000000001</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.61738</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.69079</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.99209</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1.33333</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.41388</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.9987200000000001</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.98711</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.98802</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.56121</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.55597</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.94343</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.10098</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.02042</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.79279</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.65757</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.64757</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.73629</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.80924</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.29278</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.76091</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.351</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.48403</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.15552</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.98202</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.64757</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.63257</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.6653</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.67766</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.67274</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.64951</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.67257</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.20682</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.7077</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.7881</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.70406</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.71242</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.71982</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.63908</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.75411</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.01944</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.12881</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.69878</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.70642</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.7008</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.78509</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.72994</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.8190599999999999</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.6703</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.4649</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>1.19754</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.5767</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.69074</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.56604</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.59934</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34408</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.5609700000000001</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.71188</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.29454</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.58649</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.65989</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.39196</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.5984400000000001</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.57023</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.6842699999999999</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.65977</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.6577000000000001</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.57985</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.33886</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.55165</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39734</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.42739</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.75236</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.49523</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.5131</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.5216799999999999</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28466</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.34355</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.40784</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.45321</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.92901</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.48308</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.18814</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.90054</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.7665299999999999</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.44965</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.39544</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.45672</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.50004</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.49955</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.45011</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.48974</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34925</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35547</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.38244</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.40549</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.40581</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.55161</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.39967</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.3744</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34317</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.38686</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.44965</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.7524</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.42929</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.51755</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.70112</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.49955</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.40711</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.41974</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.42823</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5663400000000001</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38956</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.42594</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.45477</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35221</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.40123</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.6628500000000001</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.44981</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.44584</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37782</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40107</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38387</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37673</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6411</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.46781</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.39126</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.44708</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.38212</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.345</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.6333300000000001</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.59794</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.5929</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1.03766</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.58123</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.5211</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.49137</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.43614</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.45746</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.43379</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.37618</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.43877</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.51616</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.4201</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.55186</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.7607699999999999</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.36087</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.76637</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.27861</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.48259</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.39407</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.54431</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.5008899999999999</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.36083</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.73598</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.7608400000000001</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.55286</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.5009</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.45011</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.01799</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.48249</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.45582</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.10447</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.13351</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.09198</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.39174</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.12144</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.13863</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.02755</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.20298</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.15087</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.13884</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.19433</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.8510599999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.19921</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.85603</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.3534</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.9011</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.71577</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.7531599999999999</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.96216</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.5113</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.65191</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.64161</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.69168</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.5540700000000001</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36002</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.75985</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.412</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.59961</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.42812</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.6275299999999999</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.81502</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.8058</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.64006</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.62221</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.7533200000000001</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.7689600000000001</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.7729</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.63818</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.78343</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.64259</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.7612000000000001</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.59169</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.53196</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.53747</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.53747</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.59196</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.45902</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.54638</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.46453</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.71374</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.59339</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.5466</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.80067</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.61088</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.10789</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.7938</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.39902</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.75905</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.29424</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.3575</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.73595</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.66107</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.36636</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>1.00196</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.60595</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.49952</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.49954</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.55045</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.59882</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.7500800000000001</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.19831</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.70469</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.93647</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.68028</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.95811</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.89775</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.76006</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.72973</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.18218</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.18568</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.44674</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.26489</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.66841</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.25041</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.29556</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.1129</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.4364</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1.0437</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.85482</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.80471</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.44259</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.27441</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.67636</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.48964</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.5534199999999999</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.46962</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42848</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.4016</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40804</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38922</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.3666</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.44987</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40565</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.53177</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.3956</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.53323</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.79852</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.6834199999999999</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.6558200000000001</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.50483</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>1.08516</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.69245</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.66433</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.8057300000000001</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.08109</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.19264</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.49988</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.19262</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.54291</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.15301</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.55447</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.42007</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.49926</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.23285</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.3733399999999999</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.42914</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.48085</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.45006</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.5000899999999999</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.45084</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.45003</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.38343</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.42002</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.52228</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.5174299999999999</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.6009</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38084</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39214</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38141</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.75973</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.13725</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.80049</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.68035</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.47843</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.43255</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.4023</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.39839</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35842</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.39984</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.38046</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.4194</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.35232</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.42047</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.44921</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.39745</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.49864</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.36724</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.45984</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.34385</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.44957</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.39984</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.40067</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.4187</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.44975</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.59372</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.48334</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.4622</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.46312</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.44969</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.46058</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.34433</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.55261</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.38773</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.44974</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.42067</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39366</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.40865</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.46087</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.41982</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.46906</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.61639</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.58721</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.59161</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.60972</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.5716100000000001</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.46207</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.42471</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.38736</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.38786</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.97689</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.45954</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.61256</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.46161</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.46857</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.55261</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.54671</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.54161</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.54161</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.33482</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.37193</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.38178</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.23361</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.30722</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.27124</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.38775</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.38741</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.29975</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.30548</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.15287</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.73515</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.21402</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.38645</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.30062</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.27229</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.13973</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.41323</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.37886</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.35329</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.69801</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.5741499999999999</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.30539</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.30539</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.28908</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.49856</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.38652</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.38755</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.39157</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.6576900000000001</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.36617</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.39217</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.35334</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.36703</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.38269</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.37182</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.39966</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.38258</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.42363</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.4353</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.43287</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.39787</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.39283</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.38277</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.39289</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38226</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.42856</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.80716</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.38341</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.46749</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.39292</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.3889</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.38888</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.38558</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.40221</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.48935</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.1003</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.38108</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1.05738</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.97254</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.52477</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.7592100000000001</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.75902</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.5145299999999999</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.41673</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.42905</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.42614</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.40816</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.39406</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.38733</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.44414</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.55716</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.42556</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.3874</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.44309</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.62009</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>1.07301</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.42429</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.68771</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.8042</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.45415</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.40298</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.75926</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.41067</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.52777</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.40025</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.40464</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.24204</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.08648</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.98434</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.31408</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.63437</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.5491</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.38821</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.49626</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.58178</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.75866</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.55006</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.5486599999999999</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.39679</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.22528</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.7585499999999999</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.75873</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.5827899999999999</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.4503</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.49726</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>1.01051</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.7693</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.6264999999999999</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.75873</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.20172</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.6075700000000001</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.7499</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.6386799999999999</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.2655</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.9000900000000001</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.88458</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.9049400000000001</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.92336</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.17452</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.65023</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.9580700000000001</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.69371</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.98391</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.65531</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.67572</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.75789</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.65531</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.26262</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.0437</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1.02471</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.0336</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.5451</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.36155</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.056</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.41066</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.3816000000000001</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.75946</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.39005</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.34545</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.5587300000000001</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.80744</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.54944</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.75719</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.75948</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.5611900000000001</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.47012</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.45953</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40812</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.42881</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.4198</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34817</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.34477</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.36724</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.35755</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.38151</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.41976</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.40306</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.42627</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.63542</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.56068</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.54231</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.45175</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.48012</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.55996</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.81672</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.1754</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.14092</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.05191</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.15341</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.75495</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.7439</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.06034</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.08429</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.68447</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.55516</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.56171</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.5617000000000001</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.4795</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.30632</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.48376</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.54936</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.55015</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.54535</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.66099</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.5538</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>1.0505</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.66051</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.54937</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.49945</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.4995</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.48219</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.49953</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.48206</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.49957</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.57772</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.55732</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.5612</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.49956</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.51375</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.40321</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.38436</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.42325</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.5013</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.5611799999999999</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.66101</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.17353</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>1.07615</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.66108</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.58214</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.17323</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.8706499999999999</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.6610499999999999</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.15981</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.83816</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.49958</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.5115299999999999</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.49956</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.44023</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.5350900000000001</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.39145</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.39946</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34473</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36934</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.91999</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.69178</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.69924</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1.00703</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.67922</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.48061</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.40541</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.39881</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.41977</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.41004</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.39292</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.37911</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.36401</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.35385</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.3622</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38675</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.62924</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.5884299999999999</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.42284</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.64161</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.03731</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.26773</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.9342999999999999</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.98509</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.03292</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.9758300000000001</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.9433400000000001</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.97385</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.95682</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.9414600000000001</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.95141</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.44828</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.80862</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>1.16081</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.72912</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>1.15723</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>1.24236</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>1.22383</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.7273999999999999</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.94694</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.86738</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.9343400000000001</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.54862</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.72699</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.75109</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.77435</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.22316</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.09207</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.02983</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.41848</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.33943</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.02588</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.10389</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.9299299999999999</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.7645</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.76259</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.82078</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.70716</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42426</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.7000299999999999</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.5721499999999999</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40528</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.46029</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.69253</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.7407</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.6990700000000001</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.41518</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.369</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.75975</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.3903</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3766</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36872</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37113</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.40346</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.38857</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36714</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.70914</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.46586</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.74876</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.5236499999999999</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.50993</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>1.02257</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.92057</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.03311</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.93111</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>1.05111</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>1.03011</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>1.02811</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.30438</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.09397</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1.22994</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.5876699999999999</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.37913</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.68031</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.6233300000000001</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.73513</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.72146</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.02316</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.721</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.77241</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.14597</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.35729</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.57351</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.7905</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.34196</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.49779</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>1.10024</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.53741</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.49616</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.56871</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.56936</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39893</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.8136100000000001</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.76855</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.80799</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.70996</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.3756</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.26742</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.46787</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38835</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37057</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36784</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35536</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.7594</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.43993</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.42327</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.37452</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.37726</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.35755</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.38107</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.37289</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.49961</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38186</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.80972</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.31129</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.00239</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.9274</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.95439</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.03611</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.16523</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.06996</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.87288</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.69101</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.23327</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.21116</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.21373</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.15153</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.8663099999999999</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.70164</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.09235</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.35782</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.10291</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.10329</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.13009</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.10222</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.51754</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.19752</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.6575299999999999</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.57947</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.15172</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.7457699999999999</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.6720900000000001</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1.17543</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.87024</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.08324</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>1.07451</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.11206</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.03596</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.06722</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>1.11505</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.04751</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.05941</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.17519</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.16171</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.27656</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.19661</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.2978</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.16844</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.20248</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.11831</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.09978</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.12513</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.17533</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1.19215</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.17535</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>1.11355</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.6902999999999999</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.62771</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.57598</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.5567000000000001</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.44929</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37619</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.55235</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.31124</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.3112</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.0661</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.48129</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.5202899999999999</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.3986</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.46876</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.46752</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.48633</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.5023</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.48754</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39314</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38495</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.49483</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.48874</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.4872</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.48418</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.48663</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.47877</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.46712</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.46569</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.45729</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.46342</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.37225</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.84797</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.46371</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.37404</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.57692</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.70092</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.71628</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.66723</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.9460599999999999</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.75963</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.95917</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.17289</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.30877</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.44809</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.43731</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.46654</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.54861</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1.26374</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.85038</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.77689</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.7325199999999999</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.7067599999999999</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1.51175</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.8495199999999999</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.9168200000000001</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.22259</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.80188</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.5993999999999999</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.64054</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.73458</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.62421</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.7387400000000001</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.60736</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1.18545</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.17867</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.41388</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.17884</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.17516</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>1.17509</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>1.09119</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.06528</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>1.17966</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1.08534</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>1.17508</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1.04366</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>1.06863</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>1.19316</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.08339</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.54207</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.8073400000000001</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.80341</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.5642699999999999</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.38071</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.20028</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.84834</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.84833</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.55886</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.55416</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.56212</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.51528</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.5534600000000001</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41936</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.52083</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.50082</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37304</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.45945</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.45945</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.43855</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38071</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.41225</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.49513</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.50004</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.54776</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.52088</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.52086</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.5571200000000001</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.1751</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.88276</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.49303</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>1.17074</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.5088</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.57013</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.8439</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.79483</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.5968300000000001</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.8518</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.50281</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.52106</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.5443300000000001</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.17519</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.69953</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.55565</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.1818</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.54935</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.54896</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.58124</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.79947</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.55468</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.79828</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.8496900000000001</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1.17418</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.7994199999999999</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.68341</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>1.05009</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.1751</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1.17514</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.17512</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.17371</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.82217</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.7312000000000001</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.6449199999999999</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.6732</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.68052</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.72615</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.82939</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.80868</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.60097</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.7991699999999999</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.7478400000000001</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1.12923</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.74495</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.60088</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.62319</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.62771</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.60085</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.6008300000000001</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.68898</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.6500900000000001</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.79969</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.6907300000000001</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.5998600000000001</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.5208200000000001</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.50082</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37241</v>
       </c>
     </row>
   </sheetData>
